--- a/naver-place-crawler/results_health/부평구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평구_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1306</v>
+        <v>1899</v>
       </c>
       <c r="Q2" t="n">
-        <v>1207</v>
+        <v>953</v>
       </c>
       <c r="R2" t="n">
-        <v>2513</v>
+        <v>2852</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle_gym02</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1882</v>
+        <v>1315</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>3057</v>
       </c>
       <c r="R3" t="n">
-        <v>2846</v>
+        <v>4372</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkdals5404</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1707</v>
+        <v>1310</v>
       </c>
       <c r="Q4" t="n">
-        <v>1511</v>
+        <v>920</v>
       </c>
       <c r="R4" t="n">
-        <v>3218</v>
+        <v>2230</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오빠네헬스장&amp;PT 부평점</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oppagym@naver.com</t>
+          <t>spoany_70@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1361-1167</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부흥로 265 501호</t>
+          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oppagym</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>768</v>
+        <v>1526</v>
       </c>
       <c r="Q5" t="n">
-        <v>2420</v>
+        <v>2034</v>
       </c>
       <c r="R5" t="n">
-        <v>3188</v>
+        <v>3560</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1538103381</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538103381</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
+          <t>rkdals5404@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany86</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1305</v>
+        <v>1707</v>
       </c>
       <c r="Q6" t="n">
-        <v>3015</v>
+        <v>1506</v>
       </c>
       <c r="R6" t="n">
-        <v>4320</v>
+        <v>3213</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플우먼 부평점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1330-3912</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
+          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1169</v>
+        <v>986</v>
       </c>
       <c r="Q7" t="n">
-        <v>914</v>
+        <v>491</v>
       </c>
       <c r="R7" t="n">
-        <v>2083</v>
+        <v>1477</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1619023009</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619023009</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>msgym_01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>032-330-3334</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천광역시 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/msgym_01/223768835115</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>983</v>
+        <v>895</v>
       </c>
       <c r="Q8" t="n">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="R8" t="n">
-        <v>1465</v>
+        <v>1353</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1350569862</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1350569862</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>874</v>
+        <v>801</v>
       </c>
       <c r="Q9" t="n">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="R9" t="n">
-        <v>1323</v>
+        <v>1234</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>카우짐 백운역점</t>
+          <t>무무바디짐 부평점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cowgym_24@naver.com</t>
+          <t>qudan79@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1370-4255</t>
+          <t>0507-1440-0638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
+          <t>인천광역시 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>792</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>432</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1224</v>
+        <v>28</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1852598877</t>
+          <t>2061355439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
+          <t>https://m.place.naver.com/place/2061355439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q11" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="R11" t="n">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평구_헬스장.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
+          <t>spoany_70@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany86</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1315</v>
+        <v>1527</v>
       </c>
       <c r="Q3" t="n">
-        <v>3057</v>
+        <v>2033</v>
       </c>
       <c r="R3" t="n">
-        <v>4372</v>
+        <v>3560</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="Q4" t="n">
-        <v>920</v>
+        <v>3061</v>
       </c>
       <c r="R4" t="n">
-        <v>2230</v>
+        <v>4377</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 부평시장역점</t>
+          <t>짐박스피트니스 부평시장역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany_70@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1428-9618</t>
+          <t>0507-1471-0163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
+          <t>인천광역시 부평구 부흥로 277 1~4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_70</t>
+          <t>https://gymboxx.com/onceinayear?gym=72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1526</v>
+        <v>2048</v>
       </c>
       <c r="Q5" t="n">
-        <v>2034</v>
+        <v>74</v>
       </c>
       <c r="R5" t="n">
-        <v>3560</v>
+        <v>2122</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1163734622</t>
+          <t>1569809175</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163734622</t>
+          <t>https://m.place.naver.com/place/1569809175</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkdals5404</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1707</v>
+        <v>1310</v>
       </c>
       <c r="Q6" t="n">
-        <v>1506</v>
+        <v>920</v>
       </c>
       <c r="R6" t="n">
-        <v>3213</v>
+        <v>2230</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>986</v>
+        <v>710</v>
       </c>
       <c r="Q7" t="n">
-        <v>491</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>1477</v>
+        <v>1001</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>895</v>
+        <v>986</v>
       </c>
       <c r="Q8" t="n">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="R8" t="n">
-        <v>1353</v>
+        <v>1478</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>카우짐 백운역점</t>
+          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cowgym_24@naver.com</t>
+          <t>msgym_01@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1370-4255</t>
+          <t>032-330-3334</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
+          <t>인천광역시 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
+          <t>https://blog.naver.com/msgym_01/223768835115</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>801</v>
+        <v>899</v>
       </c>
       <c r="Q9" t="n">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="R9" t="n">
-        <v>1234</v>
+        <v>1357</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1852598877</t>
+          <t>1350569862</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
+          <t>https://m.place.naver.com/place/1350569862</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,34 +1320,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>무무바디짐 부평점</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qudan79@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1440-0638</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1358 2층</t>
+          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qudan79</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1369,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>801</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>433</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>1234</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2061355439</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061355439</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1409,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3세트짐 체형교정센터 부평본점</t>
+          <t>무무바디짐 부평점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lineup_pt@naver.com</t>
+          <t>qudan79@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1323-8788</t>
+          <t>0507-1440-0638</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1404 1003호</t>
+          <t>인천광역시 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lineup_pt</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,17 +1467,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>369</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>456</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>825</v>
+        <v>28</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1774897291</t>
+          <t>2061355439</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774897291</t>
+          <t>https://m.place.naver.com/place/2061355439</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부평구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평구_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="Q2" t="n">
         <v>953</v>
       </c>
       <c r="R2" t="n">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1038,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>710</v>
+        <v>986</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>492</v>
       </c>
       <c r="R7" t="n">
-        <v>1001</v>
+        <v>1478</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>msgym_01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>032-330-3334</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천광역시 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/msgym_01/223768835115</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>986</v>
+        <v>899</v>
       </c>
       <c r="Q8" t="n">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="R8" t="n">
-        <v>1478</v>
+        <v>1357</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1350569862</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1350569862</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>899</v>
+        <v>801</v>
       </c>
       <c r="Q9" t="n">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="R9" t="n">
-        <v>1357</v>
+        <v>1234</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,34 +1320,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>카우짐 백운역점</t>
+          <t>무무바디짐 부평점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cowgym_24@naver.com</t>
+          <t>qudan79@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1370-4255</t>
+          <t>0507-1440-0638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
+          <t>인천광역시 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>801</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>433</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1234</v>
+        <v>28</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1852598877</t>
+          <t>2061355439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
+          <t>https://m.place.naver.com/place/2061355439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>무무바디짐 부평점</t>
+          <t>그루비짐24 헬스PT 갈산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>qudan79@naver.com</t>
+          <t>groovygs2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1440-0638</t>
+          <t>0507-1379-2744</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로 1358 2층</t>
+          <t>인천광역시 부평구 굴포로 42 지하층 B01호, B02호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qudan79</t>
+          <t>https://www.instagram.com/groovygym24_gs/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,17 +1467,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>815</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>839</v>
       </c>
       <c r="R11" t="n">
-        <v>28</v>
+        <v>1654</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2061355439</t>
+          <t>1574242499</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061355439</t>
+          <t>https://m.place.naver.com/place/1574242499</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부평구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 339 2층</t>
+          <t>인천 부평구 부평북로 339 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fs9p</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="Q3" t="n">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="R3" t="n">
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="Q4" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="R4" t="n">
-        <v>3566</v>
+        <v>3567</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -907,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="Q5" t="n">
         <v>74</v>
       </c>
       <c r="R5" t="n">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -932,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="Q6" t="n">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="R6" t="n">
-        <v>4383</v>
+        <v>4382</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>rkdals5404@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1311</v>
+        <v>1706</v>
       </c>
       <c r="Q7" t="n">
-        <v>920</v>
+        <v>1505</v>
       </c>
       <c r="R7" t="n">
-        <v>2231</v>
+        <v>3211</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>휘트니스피플우먼 부평점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1330-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,13 +1178,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44qaq</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>710</v>
+        <v>1181</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>924</v>
       </c>
       <c r="R8" t="n">
-        <v>1001</v>
+        <v>2105</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1619023009</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1619023009</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1294,10 @@
         <v>986</v>
       </c>
       <c r="Q9" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R9" t="n">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1308,41 +1316,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>3세트짐 체형교정센터 부평본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>lineup_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1323-8788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 체육관로 34 7층</t>
+          <t>인천 부평구 경원대로 1404 1003호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>https://blog.naver.com/lineup_pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1370,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq6k9</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>899</v>
+        <v>369</v>
       </c>
       <c r="Q10" t="n">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="R10" t="n">
-        <v>1358</v>
+        <v>825</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,205 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1774897291</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1774897291</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>카우짐 백운역점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>cowgym_24@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1370-4255</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>인천광역시 부평구 마장로 75 대경빌딩 B1층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>801</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>433</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1234</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1852598877</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>온정필라테스&amp;PT 산곡점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ktg191800@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ktg191800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lmji</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>328</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>609</v>
-      </c>
-      <c r="R12" t="n">
-        <v>937</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1452652224</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1452652224</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
